--- a/docs/Mapping_casi_uso/cittadinanza/Citt_011.xlsx
+++ b/docs/Mapping_casi_uso/cittadinanza/Citt_011.xlsx
@@ -687,7 +687,7 @@
         <v>13</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>10</v>
